--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -7945,7 +7945,7 @@
         <v>120540898</v>
       </c>
       <c r="B64" t="n">
-        <v>58057</v>
+        <v>58110</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96679</v>
+        <v>96682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96682</v>
+        <v>96683</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96683</v>
+        <v>96688</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>120540898</v>
       </c>
       <c r="B64" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ85"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9048,27 +9048,27 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133593374</v>
+        <v>136959106</v>
       </c>
       <c r="B74" t="n">
-        <v>57972</v>
+        <v>58008</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9076,25 +9076,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pråmviken, Mpd</t>
+          <t>Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>634287</v>
+        <v>634152</v>
       </c>
       <c r="R74" t="n">
-        <v>6902366</v>
+        <v>6903216</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9118,22 +9129,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9148,27 +9149,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kerstin Stickler</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kerstin Stickler</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133593374</t>
+          <t>https://artportalen.se/Sighting/136959106</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129730828</v>
+        <v>133593374</v>
       </c>
       <c r="B75" t="n">
-        <v>57899</v>
+        <v>57972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9176,16 +9177,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9194,6 +9195,11 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Pråmviken, Mpd</t>
@@ -9230,22 +9236,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9271,16 +9277,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129730828</t>
+          <t>https://artportalen.se/Sighting/133593374</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126201679</v>
+        <v>129730828</v>
       </c>
       <c r="B76" t="n">
-        <v>99153</v>
+        <v>57899</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9288,33 +9294,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219874</v>
+        <v>100067</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pråmviken, Mpd</t>
@@ -9351,22 +9348,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9392,16 +9389,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126201679</t>
+          <t>https://artportalen.se/Sighting/129730828</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134669910</v>
+        <v>126201679</v>
       </c>
       <c r="B77" t="n">
-        <v>106324</v>
+        <v>99153</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9409,31 +9406,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9477,22 +9469,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9518,63 +9510,68 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134669910</t>
+          <t>https://artportalen.se/Sighting/126201679</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123284491</v>
+        <v>134669910</v>
       </c>
       <c r="B78" t="n">
-        <v>80305</v>
+        <v>106324</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>392</v>
+        <v>221144</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bränningen, Mpd</t>
+          <t>Pråmviken, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>602025</v>
+        <v>634287</v>
       </c>
       <c r="R78" t="n">
-        <v>6901155</v>
+        <v>6902366</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9593,37 +9590,27 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Attmar</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>1393</t>
+          <t>Njurunda</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>på ett hygge</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9638,58 +9625,54 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Kerstin Stickler</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Kerstin Stickler</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123284491</t>
+          <t>https://artportalen.se/Sighting/134669910</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123325626</v>
+        <v>123284491</v>
       </c>
       <c r="B79" t="n">
-        <v>80432</v>
+        <v>80305</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9703,10 +9686,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602019</v>
+        <v>602025</v>
       </c>
       <c r="R79" t="n">
-        <v>6901151</v>
+        <v>6901155</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9733,7 +9716,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -9743,7 +9726,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9753,12 +9736,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>på ett hygge</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9778,7 +9761,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9788,16 +9771,16 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123325626</t>
+          <t>https://artportalen.se/Sighting/123284491</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1935699</v>
+        <v>123325626</v>
       </c>
       <c r="B80" t="n">
-        <v>75428</v>
+        <v>80432</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,37 +9788,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Salen, Mpd</t>
+          <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>635278</v>
+        <v>602019</v>
       </c>
       <c r="R80" t="n">
-        <v>6899522</v>
+        <v>6901151</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9854,17 +9846,37 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Njurunda</t>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2008-05-08</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2008-05-08</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9879,24 +9891,28 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Andreas Karlberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1935699</t>
+          <t>https://artportalen.se/Sighting/123325626</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1935700</v>
+        <v>1935699</v>
       </c>
       <c r="B81" t="n">
         <v>75428</v>
@@ -9924,26 +9940,17 @@
           <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Salen, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>635282</v>
+        <v>635278</v>
       </c>
       <c r="R81" t="n">
-        <v>6899527</v>
+        <v>6899522</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10001,13 +10008,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1935700</t>
+          <t>https://artportalen.se/Sighting/1935699</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1935701</v>
+        <v>1935700</v>
       </c>
       <c r="B82" t="n">
         <v>75428</v>
@@ -10037,7 +10044,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10051,7 +10058,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>635288</v>
+        <v>635282</v>
       </c>
       <c r="R82" t="n">
         <v>6899527</v>
@@ -10112,16 +10119,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1935701</t>
+          <t>https://artportalen.se/Sighting/1935700</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>85250968</v>
+        <v>1935701</v>
       </c>
       <c r="B83" t="n">
-        <v>58114</v>
+        <v>75428</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10129,46 +10136,43 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Salens NR, Mpd</t>
+          <t>Salen, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>635537</v>
+        <v>635288</v>
       </c>
       <c r="R83" t="n">
-        <v>6900219</v>
+        <v>6899527</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10195,22 +10199,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2020-05-09</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2008-05-08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2020-05-09</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2008-05-08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10225,27 +10219,27 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Andreas Karlberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85250968</t>
+          <t>https://artportalen.se/Sighting/1935701</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136130914</v>
+        <v>85250968</v>
       </c>
       <c r="B84" t="n">
-        <v>89472</v>
+        <v>58114</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10253,37 +10247,49 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lappmon, Mpd</t>
+          <t>Salens NR, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>603206</v>
+        <v>635537</v>
       </c>
       <c r="R84" t="n">
-        <v>6897616</v>
+        <v>6900219</v>
       </c>
       <c r="S84" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10302,27 +10308,27 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>Attmar</t>
+          <t>Njurunda</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2020-05-09</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2020-05-09</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10337,81 +10343,65 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sara Widell</t>
+          <t>Sven Jägbrant</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sara Widell</t>
+          <t>Sven Jägbrant</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136130914</t>
+          <t>https://artportalen.se/Sighting/85250968</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>81919158</v>
+        <v>136130914</v>
       </c>
       <c r="B85" t="n">
-        <v>57144</v>
+        <v>89472</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102613</v>
+        <v>510</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Armsjötorpet vägen nerströms , Mpd</t>
+          <t>Lappmon, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>626692</v>
+        <v>603206</v>
       </c>
       <c r="R85" t="n">
-        <v>6893681</v>
+        <v>6897616</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10430,27 +10420,27 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Njurunda</t>
+          <t>Attmar</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10465,16 +10455,144 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Rode Nordin</t>
+          <t>Sara Widell</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Rode Nordin, Bruno Nordin</t>
+          <t>Sara Widell</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136130914</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>81919158</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Armsjötorpet vägen nerströms , Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>626692</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6893681</v>
+      </c>
+      <c r="S86" t="n">
+        <v>8</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81919158</t>
         </is>
@@ -10566,6 +10684,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9048,10 +9048,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136959106</v>
+        <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>58008</v>
+        <v>93454</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9059,39 +9059,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9099,10 +9086,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>634152</v>
+        <v>634356</v>
       </c>
       <c r="R74" t="n">
-        <v>6903216</v>
+        <v>6903233</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9129,12 +9116,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9143,6 +9130,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9160,33 +9148,33 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136959106</t>
+          <t>https://artportalen.se/Sighting/137014205</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133593374</v>
+        <v>136959106</v>
       </c>
       <c r="B75" t="n">
-        <v>57972</v>
+        <v>58008</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9194,25 +9182,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Pråmviken, Mpd</t>
+          <t>Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>634287</v>
+        <v>634152</v>
       </c>
       <c r="R75" t="n">
-        <v>6902366</v>
+        <v>6903216</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9236,22 +9235,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9266,27 +9255,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kerstin Stickler</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kerstin Stickler</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133593374</t>
+          <t>https://artportalen.se/Sighting/136959106</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129730828</v>
+        <v>133593374</v>
       </c>
       <c r="B76" t="n">
-        <v>57899</v>
+        <v>57972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9294,16 +9283,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9312,6 +9301,11 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pråmviken, Mpd</t>
@@ -9348,22 +9342,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9389,16 +9383,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129730828</t>
+          <t>https://artportalen.se/Sighting/133593374</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126201679</v>
+        <v>129730828</v>
       </c>
       <c r="B77" t="n">
-        <v>99153</v>
+        <v>57899</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9406,33 +9400,24 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219874</v>
+        <v>100067</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pråmviken, Mpd</t>
@@ -9469,22 +9454,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9510,16 +9495,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126201679</t>
+          <t>https://artportalen.se/Sighting/129730828</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134669910</v>
+        <v>126201679</v>
       </c>
       <c r="B78" t="n">
-        <v>106324</v>
+        <v>99153</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9527,31 +9512,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9595,22 +9575,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9636,63 +9616,68 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134669910</t>
+          <t>https://artportalen.se/Sighting/126201679</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123284491</v>
+        <v>134669910</v>
       </c>
       <c r="B79" t="n">
-        <v>80305</v>
+        <v>106324</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>392</v>
+        <v>221144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bränningen, Mpd</t>
+          <t>Pråmviken, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>602025</v>
+        <v>634287</v>
       </c>
       <c r="R79" t="n">
-        <v>6901155</v>
+        <v>6902366</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9711,37 +9696,27 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Attmar</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>1393</t>
+          <t>Njurunda</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>på ett hygge</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9756,58 +9731,54 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Kerstin Stickler</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Kerstin Stickler</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123284491</t>
+          <t>https://artportalen.se/Sighting/134669910</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123325626</v>
+        <v>123284491</v>
       </c>
       <c r="B80" t="n">
-        <v>80432</v>
+        <v>80305</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9821,10 +9792,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>602019</v>
+        <v>602025</v>
       </c>
       <c r="R80" t="n">
-        <v>6901151</v>
+        <v>6901155</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9851,7 +9822,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2024_1394</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -9861,7 +9832,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9871,12 +9842,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Aspar på hygge, alla bålar utdöende</t>
+          <t>på ett hygge</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9896,7 +9867,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9906,16 +9877,16 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123325626</t>
+          <t>https://artportalen.se/Sighting/123284491</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1935699</v>
+        <v>123325626</v>
       </c>
       <c r="B81" t="n">
-        <v>75428</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9923,37 +9894,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Salen, Mpd</t>
+          <t>Bränningen, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>635278</v>
+        <v>602019</v>
       </c>
       <c r="R81" t="n">
-        <v>6899522</v>
+        <v>6901151</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9972,17 +9952,37 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Njurunda</t>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>2024_1394</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2008-05-08</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2008-05-08</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Aspar på hygge, alla bålar utdöende</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9997,24 +9997,28 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Andreas Karlberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1935699</t>
+          <t>https://artportalen.se/Sighting/123325626</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1935700</v>
+        <v>1935699</v>
       </c>
       <c r="B82" t="n">
         <v>75428</v>
@@ -10042,26 +10046,17 @@
           <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Salen, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>635282</v>
+        <v>635278</v>
       </c>
       <c r="R82" t="n">
-        <v>6899527</v>
+        <v>6899522</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10119,13 +10114,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1935700</t>
+          <t>https://artportalen.se/Sighting/1935699</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1935701</v>
+        <v>1935700</v>
       </c>
       <c r="B83" t="n">
         <v>75428</v>
@@ -10155,7 +10150,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10169,7 +10164,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>635288</v>
+        <v>635282</v>
       </c>
       <c r="R83" t="n">
         <v>6899527</v>
@@ -10230,16 +10225,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1935701</t>
+          <t>https://artportalen.se/Sighting/1935700</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>85250968</v>
+        <v>1935701</v>
       </c>
       <c r="B84" t="n">
-        <v>58114</v>
+        <v>75428</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10247,46 +10242,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Salens NR, Mpd</t>
+          <t>Salen, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>635537</v>
+        <v>635288</v>
       </c>
       <c r="R84" t="n">
-        <v>6900219</v>
+        <v>6899527</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10313,22 +10305,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2020-05-09</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2008-05-08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2020-05-09</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2008-05-08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10343,27 +10325,27 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Andreas Karlberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sven Jägbrant</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85250968</t>
+          <t>https://artportalen.se/Sighting/1935701</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136130914</v>
+        <v>85250968</v>
       </c>
       <c r="B85" t="n">
-        <v>89472</v>
+        <v>58114</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10371,37 +10353,49 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lappmon, Mpd</t>
+          <t>Salens NR, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>603206</v>
+        <v>635537</v>
       </c>
       <c r="R85" t="n">
-        <v>6897616</v>
+        <v>6900219</v>
       </c>
       <c r="S85" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10420,27 +10414,27 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Attmar</t>
+          <t>Njurunda</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2020-05-09</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2020-05-09</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10455,81 +10449,65 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sara Widell</t>
+          <t>Sven Jägbrant</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sara Widell</t>
+          <t>Sven Jägbrant</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136130914</t>
+          <t>https://artportalen.se/Sighting/85250968</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>81919158</v>
+        <v>136130914</v>
       </c>
       <c r="B86" t="n">
-        <v>57144</v>
+        <v>89472</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102613</v>
+        <v>510</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Armsjötorpet vägen nerströms , Mpd</t>
+          <t>Lappmon, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>626692</v>
+        <v>603206</v>
       </c>
       <c r="R86" t="n">
-        <v>6893681</v>
+        <v>6897616</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10548,27 +10526,27 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Njurunda</t>
+          <t>Attmar</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10583,16 +10561,144 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Rode Nordin</t>
+          <t>Sara Widell</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Rode Nordin, Bruno Nordin</t>
+          <t>Sara Widell</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136130914</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>81919158</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Armsjötorpet vägen nerströms , Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>626692</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6893681</v>
+      </c>
+      <c r="S87" t="n">
+        <v>8</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81919158</t>
         </is>
@@ -10685,6 +10791,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -7945,7 +7945,7 @@
         <v>120540898</v>
       </c>
       <c r="B64" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>136959106</v>
       </c>
       <c r="B75" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -7945,7 +7945,7 @@
         <v>120540898</v>
       </c>
       <c r="B64" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>136959106</v>
       </c>
       <c r="B75" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9188,16 +9188,8 @@
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>136959106</v>
       </c>
       <c r="B75" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>136959106</v>
       </c>
       <c r="B75" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>136959106</v>
       </c>
       <c r="B75" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -9051,7 +9051,7 @@
         <v>137014205</v>
       </c>
       <c r="B74" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>136959106</v>
       </c>
       <c r="B75" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
